--- a/accton/dist/20261025_智邦模型_v0.2.1.xlsx
+++ b/accton/dist/20261025_智邦模型_v0.2.1.xlsx
@@ -6480,7 +6480,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6698,7 +6698,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6819,7 +6819,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6940,7 +6940,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7061,7 +7061,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7182,7 +7182,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/accton/dist/20261025_智邦模型_v0.2.1.xlsx
+++ b/accton/dist/20261025_智邦模型_v0.2.1.xlsx
@@ -4903,7 +4903,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -4922,7 +4922,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5302,7 +5302,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5321,7 +5321,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5957,7 +5957,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5976,7 +5976,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6173,7 +6173,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6192,7 +6192,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/accton/dist/20261025_智邦模型_v0.2.1.xlsx
+++ b/accton/dist/20261025_智邦模型_v0.2.1.xlsx
@@ -6461,26 +6461,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6679,26 +6679,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6800,26 +6800,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6921,26 +6921,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7042,26 +7042,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7163,26 +7163,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -32998,7 +32998,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>33</v>
